--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:49:58+00:00</t>
+    <t>2026-10-29T11:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:54:13+00:00</t>
+    <t>2026-10-29T12:12:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:12:40+00:00</t>
+    <t>2026-10-29T12:15:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:15:14+00:00</t>
+    <t>2026-10-29T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:17:57+00:00</t>
+    <t>2026-10-29T12:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:25:30+00:00</t>
+    <t>2026-10-29T12:29:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:29:08+00:00</t>
+    <t>2026-10-29T12:36:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:36:03+00:00</t>
+    <t>2026-10-29T12:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:50:53+00:00</t>
+    <t>2026-10-29T13:31:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:31:58+00:00</t>
+    <t>2026-10-29T13:46:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:46:42+00:00</t>
+    <t>2026-10-29T13:53:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:27+00:00</t>
+    <t>2026-10-29T13:59:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stockholm-genomic-device.xlsx
+++ b/StructureDefinition-stockholm-genomic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:59:37+00:00</t>
+    <t>2026-10-30T08:47:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
